--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
   <si>
     <t>Filename</t>
   </si>
@@ -811,16 +811,16 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.8854,0.0200,0.0305,0.0102</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.8870,0.0004,0.0005,0.0967</t>
-  </si>
-  <si>
-    <t>0.0375,0.0001,0.0001,0.9894</t>
+    <t>0.9736,0.0022,0.0072,0.0013</t>
+  </si>
+  <si>
+    <t>0.0021,0.0006,0.0000,0.9993</t>
+  </si>
+  <si>
+    <t>0.9487,0.0004,0.0009,0.0316</t>
+  </si>
+  <si>
+    <t>0.1290,0.0003,0.0004,0.9501</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
@@ -835,664 +835,667 @@
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2562,0.0021,0.7946,0.0002</t>
+  </si>
+  <si>
+    <t>0.1657,0.0011,0.8657,0.0002</t>
+  </si>
+  <si>
+    <t>0.7059,0.0007,0.4431,0.0001</t>
+  </si>
+  <si>
+    <t>0.0868,0.0006,0.9168,0.0004</t>
+  </si>
+  <si>
+    <t>0.7252,0.0016,0.2679,0.0018</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0488,0.9463,0.0068,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5792,0.0005,0.4781,0.0010</t>
+  </si>
+  <si>
+    <t>0.6395,0.0017,0.4178,0.0007</t>
+  </si>
+  <si>
+    <t>0.0303,0.0005,0.9740,0.0001</t>
+  </si>
+  <si>
+    <t>0.0196,0.0004,0.9755,0.0003</t>
+  </si>
+  <si>
+    <t>0.0398,0.0001,0.9765,0.0000</t>
+  </si>
+  <si>
+    <t>0.1047,0.0001,0.8876,0.0014</t>
+  </si>
+  <si>
+    <t>0.0115,0.0000,0.9908,0.0003</t>
+  </si>
+  <si>
+    <t>0.1621,0.8149,0.0113,0.0001</t>
+  </si>
+  <si>
+    <t>0.6322,0.0330,0.2971,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.0006,0.9990,0.0007</t>
+  </si>
+  <si>
+    <t>0.0052,0.9889,0.0080,0.0001</t>
+  </si>
+  <si>
+    <t>0.9813,0.0077,0.0034,0.0003</t>
+  </si>
+  <si>
+    <t>0.9699,0.0060,0.0133,0.0004</t>
+  </si>
+  <si>
+    <t>0.6644,0.4664,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.0036,0.9712,0.1258,0.0001</t>
+  </si>
+  <si>
+    <t>0.0329,0.8001,0.0927,0.0003</t>
+  </si>
+  <si>
+    <t>0.6145,0.0011,0.4660,0.0006</t>
+  </si>
+  <si>
+    <t>0.0231,0.0292,0.9492,0.0003</t>
+  </si>
+  <si>
+    <t>0.3214,0.0001,0.7676,0.0002</t>
+  </si>
+  <si>
+    <t>0.1644,0.0022,0.8743,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.9940,0.0076,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.0054,0.9888,0.0026</t>
+  </si>
+  <si>
+    <t>0.0019,0.8912,0.0019,0.9786</t>
+  </si>
+  <si>
+    <t>0.0011,0.9979,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.9978,0.0040,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9990,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0375,0.0017,0.9480,0.0003</t>
+  </si>
+  <si>
+    <t>0.0034,0.0023,0.9929,0.0001</t>
+  </si>
+  <si>
+    <t>0.0156,0.0015,0.9664,0.0079</t>
+  </si>
+  <si>
+    <t>0.0176,0.0000,0.9908,0.0000</t>
+  </si>
+  <si>
+    <t>0.0051,0.0003,0.9935,0.0003</t>
+  </si>
+  <si>
+    <t>0.0038,0.0019,0.9911,0.0005</t>
+  </si>
+  <si>
+    <t>0.9887,0.0126,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.0008,0.9987,0.0005</t>
+  </si>
+  <si>
+    <t>0.9978,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0014,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9863,0.0152,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9831,0.2288,0.0001</t>
+  </si>
+  <si>
+    <t>0.0050,0.0032,0.9884,0.0006</t>
+  </si>
+  <si>
+    <t>0.0198,0.0092,0.9621,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9902,0.4975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.9958,0.0032,0.0000</t>
+  </si>
+  <si>
+    <t>0.8639,0.0008,0.1834,0.0003</t>
+  </si>
+  <si>
+    <t>0.8088,0.0108,0.1638,0.0006</t>
+  </si>
+  <si>
+    <t>0.0041,0.0027,0.9945,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9959,0.8209,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.9521,0.2739,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.0704,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9908,0.6744,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0001,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0008,0.0004,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0002,0.9966,0.0790,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.8810,0.9307,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9779,0.9273,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9912,0.6479,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9819,0.7013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9450,0.7425,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9995,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.6520,0.0074,0.3310,0.0016</t>
-  </si>
-  <si>
-    <t>0.0510,0.0050,0.9271,0.0006</t>
-  </si>
-  <si>
-    <t>0.0902,0.0003,0.9397,0.0000</t>
-  </si>
-  <si>
-    <t>0.0312,0.0006,0.9699,0.0001</t>
-  </si>
-  <si>
-    <t>0.9515,0.0004,0.0645,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9979,0.0037,0.0000</t>
-  </si>
-  <si>
-    <t>0.0628,0.9273,0.0094,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8723,0.0014,0.1434,0.0006</t>
-  </si>
-  <si>
-    <t>0.4583,0.0011,0.6115,0.0007</t>
-  </si>
-  <si>
-    <t>0.0095,0.0004,0.9875,0.0003</t>
-  </si>
-  <si>
-    <t>0.0513,0.0010,0.9444,0.0003</t>
-  </si>
-  <si>
-    <t>0.6333,0.0001,0.5083,0.0002</t>
-  </si>
-  <si>
-    <t>0.0378,0.0001,0.9608,0.0005</t>
-  </si>
-  <si>
-    <t>0.0059,0.0000,0.9951,0.0002</t>
-  </si>
-  <si>
-    <t>0.2537,0.7248,0.0138,0.0003</t>
-  </si>
-  <si>
-    <t>0.8826,0.0269,0.0589,0.0016</t>
-  </si>
-  <si>
-    <t>0.0007,0.0007,0.9991,0.0007</t>
-  </si>
-  <si>
-    <t>0.0138,0.9708,0.0138,0.0001</t>
-  </si>
-  <si>
-    <t>0.9706,0.0138,0.0047,0.0009</t>
-  </si>
-  <si>
-    <t>0.9527,0.0321,0.0107,0.0002</t>
-  </si>
-  <si>
-    <t>0.8575,0.2146,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.0073,0.9646,0.0825,0.0001</t>
-  </si>
-  <si>
-    <t>0.1726,0.2334,0.2155,0.0004</t>
-  </si>
-  <si>
-    <t>0.5522,0.0014,0.5440,0.0004</t>
-  </si>
-  <si>
-    <t>0.1121,0.0050,0.8767,0.0004</t>
-  </si>
-  <si>
-    <t>0.0599,0.0005,0.9312,0.0005</t>
-  </si>
-  <si>
-    <t>0.0403,0.0068,0.9557,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9984,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0036,0.0006,0.9903,0.0018</t>
-  </si>
-  <si>
-    <t>0.0404,0.7022,0.0017,0.6416</t>
-  </si>
-  <si>
-    <t>0.0014,0.9979,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.9984,0.0048,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0036,0.0026,0.9892,0.0002</t>
-  </si>
-  <si>
-    <t>0.0172,0.0240,0.9560,0.0002</t>
-  </si>
-  <si>
-    <t>0.0034,0.0001,0.9943,0.0006</t>
-  </si>
-  <si>
-    <t>0.0622,0.0001,0.9688,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0001,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.9955,0.0047,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0011,0.0002,0.0001</t>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0039,0.0000,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0270,0.0005,0.9720,0.0002</t>
+  </si>
+  <si>
+    <t>0.9715,0.0007,0.0120,0.0004</t>
+  </si>
+  <si>
+    <t>0.0037,0.0001,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9987,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9994,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.9954,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0176,0.9779,0.0038,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.9982,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3333,0.7173,0.0086,0.0004</t>
+  </si>
+  <si>
+    <t>0.8201,0.0182,0.1308,0.0016</t>
+  </si>
+  <si>
+    <t>0.1362,0.0056,0.8356,0.0010</t>
+  </si>
+  <si>
+    <t>0.8544,0.0106,0.0994,0.0015</t>
+  </si>
+  <si>
+    <t>0.8348,0.0025,0.2099,0.0004</t>
+  </si>
+  <si>
+    <t>0.0486,0.3483,0.0307,0.8993</t>
+  </si>
+  <si>
+    <t>0.0004,0.9985,0.0052,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0007,0.0040</t>
+  </si>
+  <si>
+    <t>0.0000,0.9946,0.8903,0.0000</t>
+  </si>
+  <si>
+    <t>0.0048,0.9921,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.6625,0.4880,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.7646,0.3286,0.0063,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0006,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.7691,0.8677,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.3019,0.9518,0.0000</t>
+  </si>
+  <si>
+    <t>0.0129,0.0090,0.9690,0.0000</t>
+  </si>
+  <si>
+    <t>0.0136,0.0014,0.9793,0.0001</t>
+  </si>
+  <si>
+    <t>0.9738,0.0007,0.0091,0.0003</t>
+  </si>
+  <si>
+    <t>0.6762,0.0017,0.3703,0.0009</t>
+  </si>
+  <si>
+    <t>0.5476,0.0001,0.5396,0.0005</t>
+  </si>
+  <si>
+    <t>0.6246,0.0018,0.4055,0.0018</t>
+  </si>
+  <si>
+    <t>0.0136,0.0001,0.0001,0.9963</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9860,0.7143,0.0000</t>
+  </si>
+  <si>
+    <t>0.9967,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0413,0.9613,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0946,0.9362,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.5568,0.0001,0.0001,0.6056</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0049,0.9976,0.0010</t>
+  </si>
+  <si>
+    <t>0.9737,0.0001,0.0002,0.0176</t>
+  </si>
+  <si>
+    <t>0.9979,0.0000,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.4016,0.5470,0.0392,0.0007</t>
+  </si>
+  <si>
+    <t>0.9735,0.0036,0.0028,0.0017</t>
+  </si>
+  <si>
+    <t>0.9203,0.0362,0.0233,0.0008</t>
+  </si>
+  <si>
+    <t>0.6388,0.0370,0.2651,0.0018</t>
+  </si>
+  <si>
+    <t>0.6761,0.0155,0.2927,0.0013</t>
+  </si>
+  <si>
+    <t>0.9057,0.0618,0.0161,0.0005</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9347,0.0983,0.0049,0.0002</t>
+  </si>
+  <si>
+    <t>0.4870,0.6617,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.3930,0.7212,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0153,0.0014,0.9861,0.0013</t>
+  </si>
+  <si>
+    <t>0.9754,0.0295,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0007,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0020,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8614,0.1556,0.0186,0.0018</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.9867,0.0117,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0004,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0184,0.0069,0.9647,0.0004</t>
+  </si>
+  <si>
+    <t>0.0070,0.0002,0.9915,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.1836,0.9645,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0041,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0048,0.0001,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.3256,0.0056,0.6898,0.0012</t>
+  </si>
+  <si>
+    <t>0.1580,0.0013,0.8582,0.0009</t>
+  </si>
+  <si>
+    <t>0.7765,0.0260,0.1576,0.0022</t>
+  </si>
+  <si>
+    <t>0.2687,0.0068,0.7383,0.0004</t>
+  </si>
+  <si>
+    <t>0.2825,0.0844,0.3753,0.0004</t>
+  </si>
+  <si>
+    <t>0.8684,0.0039,0.1438,0.0005</t>
+  </si>
+  <si>
+    <t>0.8370,0.0043,0.1081,0.0064</t>
+  </si>
+  <si>
+    <t>0.4172,0.0040,0.6207,0.0010</t>
+  </si>
+  <si>
+    <t>0.0651,0.9389,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.0129,0.9869,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.3315,0.7621,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.8637,0.2388,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.2607,0.8363,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9537,0.0016,0.0225,0.0003</t>
+  </si>
+  <si>
+    <t>0.8507,0.0011,0.1968,0.0004</t>
+  </si>
+  <si>
+    <t>0.7978,0.0043,0.1873,0.0016</t>
+  </si>
+  <si>
+    <t>0.6981,0.0022,0.3191,0.0022</t>
+  </si>
+  <si>
+    <t>0.9065,0.0017,0.0790,0.0008</t>
+  </si>
+  <si>
+    <t>0.0099,0.0003,0.9898,0.0010</t>
+  </si>
+  <si>
+    <t>0.0135,0.0039,0.9682,0.0003</t>
+  </si>
+  <si>
+    <t>0.2956,0.0425,0.5908,0.0017</t>
+  </si>
+  <si>
+    <t>0.1442,0.0021,0.8680,0.0001</t>
+  </si>
+  <si>
+    <t>0.0169,0.0772,0.8771,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9931,0.0052,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9938,0.0068,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0017,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0029,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0104,0.0009,0.9851,0.0023</t>
+  </si>
+  <si>
+    <t>0.1964,0.0937,0.6077,0.0042</t>
+  </si>
+  <si>
+    <t>0.9373,0.0022,0.0141,0.0122</t>
+  </si>
+  <si>
+    <t>0.0407,0.0003,0.9757,0.0000</t>
+  </si>
+  <si>
+    <t>0.0067,0.0003,0.9955,0.0000</t>
+  </si>
+  <si>
+    <t>0.0219,0.8386,0.1789,0.0003</t>
+  </si>
+  <si>
+    <t>0.0037,0.0001,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0602,0.0010,0.9354,0.0004</t>
+  </si>
+  <si>
+    <t>0.0055,0.0005,0.9946,0.0000</t>
+  </si>
+  <si>
+    <t>0.1799,0.0012,0.8372,0.0007</t>
+  </si>
+  <si>
+    <t>0.0088,0.0013,0.9838,0.0006</t>
+  </si>
+  <si>
+    <t>0.8243,0.0023,0.1596,0.0017</t>
+  </si>
+  <si>
+    <t>0.6692,0.0023,0.3232,0.0032</t>
+  </si>
+  <si>
+    <t>0.9817,0.0002,0.0066,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0013,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9970,0.0023,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9993,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0031,0.0013,0.9974,0.0008</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9758,0.0261,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9870,0.0172,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9726,0.6719,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0061,0.9935,0.0003</t>
-  </si>
-  <si>
-    <t>0.1327,0.0048,0.8456,0.0010</t>
-  </si>
-  <si>
-    <t>0.0004,0.9757,0.4221,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9988,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9568,0.0095,0.0160,0.0004</t>
-  </si>
-  <si>
-    <t>0.4231,0.0036,0.6453,0.0005</t>
-  </si>
-  <si>
-    <t>0.0008,0.0013,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9970,0.7691,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.9474,0.2625,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.2033,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9935,0.5773,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.0002,0.9997</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0009,0.0005,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.0004,0.9970,0.0337,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9896,0.9105,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9561,0.9475,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9917,0.9484,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9523,0.7248,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9932,0.1824,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.0002,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0137,0.0002,0.9858,0.0002</t>
-  </si>
-  <si>
-    <t>0.9406,0.0014,0.0313,0.0013</t>
-  </si>
-  <si>
-    <t>0.0556,0.0004,0.9552,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.9990,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0047,0.9930,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.0058,0.9917,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.9989,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.2458,0.8003,0.0055,0.0003</t>
-  </si>
-  <si>
-    <t>0.8745,0.0029,0.1303,0.0006</t>
-  </si>
-  <si>
-    <t>0.5124,0.0007,0.5994,0.0002</t>
-  </si>
-  <si>
-    <t>0.7984,0.0203,0.1299,0.0024</t>
-  </si>
-  <si>
-    <t>0.8731,0.0135,0.0669,0.0030</t>
-  </si>
-  <si>
-    <t>0.0045,0.1583,0.0161,0.9859</t>
-  </si>
-  <si>
-    <t>0.0002,0.9988,0.0101,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.0006,0.0342</t>
-  </si>
-  <si>
-    <t>0.0014,0.9866,0.1594,0.0002</t>
-  </si>
-  <si>
-    <t>0.0067,0.9897,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.7352,0.4134,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.8133,0.2497,0.0095,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9951,0.0012,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.1079,0.9869,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.6087,0.8076,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.0009,0.9951,0.0000</t>
-  </si>
-  <si>
-    <t>0.0081,0.0009,0.9879,0.0001</t>
-  </si>
-  <si>
-    <t>0.9748,0.0008,0.0113,0.0001</t>
-  </si>
-  <si>
-    <t>0.5499,0.0023,0.4975,0.0011</t>
-  </si>
-  <si>
-    <t>0.8779,0.0001,0.1914,0.0001</t>
-  </si>
-  <si>
-    <t>0.6912,0.0013,0.3752,0.0007</t>
-  </si>
-  <si>
-    <t>0.0144,0.0001,0.0000,0.9965</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9889,0.2294,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0009,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0349,0.9653,0.0025,0.0008</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.2099,0.8473,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.2947,0.0001,0.0010,0.8049</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0021,0.9961,0.0013</t>
-  </si>
-  <si>
-    <t>0.9959,0.0001,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.4767,0.5807,0.0092,0.0003</t>
-  </si>
-  <si>
-    <t>0.9922,0.0007,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9519,0.0334,0.0047,0.0004</t>
-  </si>
-  <si>
-    <t>0.3773,0.0533,0.4431,0.0028</t>
-  </si>
-  <si>
-    <t>0.8522,0.0285,0.0893,0.0006</t>
-  </si>
-  <si>
-    <t>0.8858,0.0556,0.0210,0.0007</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8771,0.1429,0.0060,0.0008</t>
-  </si>
-  <si>
-    <t>0.3729,0.7586,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.3836,0.7465,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.9092,0.0021,0.0677,0.0008</t>
-  </si>
-  <si>
-    <t>0.9050,0.1679,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0010,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9409,0.0241,0.0199,0.0017</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.9924,0.0048,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.1120,0.0276,0.7913,0.0010</t>
-  </si>
-  <si>
-    <t>0.0019,0.0003,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.0033,0.1446,0.9619,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0006,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.1615,0.0025,0.8348,0.0009</t>
-  </si>
-  <si>
-    <t>0.0240,0.0066,0.9647,0.0004</t>
-  </si>
-  <si>
-    <t>0.7073,0.0099,0.2777,0.0022</t>
-  </si>
-  <si>
-    <t>0.3045,0.0036,0.7237,0.0005</t>
-  </si>
-  <si>
-    <t>0.0444,0.8348,0.0649,0.0005</t>
-  </si>
-  <si>
-    <t>0.7311,0.0092,0.3098,0.0004</t>
-  </si>
-  <si>
-    <t>0.8486,0.0040,0.1179,0.0026</t>
-  </si>
-  <si>
-    <t>0.0818,0.0013,0.9240,0.0002</t>
-  </si>
-  <si>
-    <t>0.0190,0.9795,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0488,0.9657,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9062,0.1420,0.0044,0.0001</t>
-  </si>
-  <si>
-    <t>0.5528,0.5965,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.1737,0.8897,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.8723,0.0272,0.0284,0.0012</t>
-  </si>
-  <si>
-    <t>0.8878,0.0004,0.1394,0.0004</t>
-  </si>
-  <si>
-    <t>0.7354,0.0032,0.0319,0.0701</t>
-  </si>
-  <si>
-    <t>0.9131,0.0078,0.0436,0.0010</t>
-  </si>
-  <si>
-    <t>0.9406,0.0032,0.0422,0.0005</t>
-  </si>
-  <si>
-    <t>0.0164,0.0007,0.9821,0.0016</t>
-  </si>
-  <si>
-    <t>0.0233,0.0075,0.9414,0.0010</t>
-  </si>
-  <si>
-    <t>0.1381,0.0108,0.8272,0.0007</t>
-  </si>
-  <si>
-    <t>0.0342,0.0017,0.9577,0.0001</t>
-  </si>
-  <si>
-    <t>0.0075,0.0183,0.9694,0.0002</t>
-  </si>
-  <si>
-    <t>0.9933,0.0062,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0047,0.0010,0.9920,0.0024</t>
-  </si>
-  <si>
-    <t>0.0441,0.0042,0.9380,0.0046</t>
-  </si>
-  <si>
-    <t>0.9402,0.0039,0.0228,0.0034</t>
-  </si>
-  <si>
-    <t>0.0083,0.0001,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0137,0.0003,0.9909,0.0001</t>
-  </si>
-  <si>
-    <t>0.0445,0.0146,0.8995,0.0011</t>
-  </si>
-  <si>
-    <t>0.0027,0.0000,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.2346,0.0007,0.8168,0.0002</t>
-  </si>
-  <si>
-    <t>0.0049,0.0001,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0911,0.0005,0.9194,0.0002</t>
-  </si>
-  <si>
-    <t>0.0109,0.0062,0.9747,0.0015</t>
-  </si>
-  <si>
-    <t>0.8437,0.0001,0.1133,0.0015</t>
-  </si>
-  <si>
-    <t>0.8706,0.0005,0.1722,0.0003</t>
-  </si>
-  <si>
-    <t>0.9769,0.0003,0.0131,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0019,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0031,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0252,0.0397,0.9091,0.0012</t>
-  </si>
-  <si>
-    <t>0.0054,0.0052,0.9856,0.0001</t>
-  </si>
-  <si>
-    <t>0.2022,0.0297,0.6477,0.0003</t>
-  </si>
-  <si>
-    <t>0.0476,0.0062,0.9319,0.0003</t>
-  </si>
-  <si>
-    <t>0.0222,0.0001,0.9843,0.0001</t>
-  </si>
-  <si>
-    <t>0.0720,0.0002,0.8979,0.0029</t>
-  </si>
-  <si>
-    <t>0.1230,0.0008,0.8640,0.0015</t>
-  </si>
-  <si>
-    <t>0.5096,0.0051,0.5074,0.0011</t>
-  </si>
-  <si>
-    <t>0.9871,0.0001,0.0002,0.0070</t>
-  </si>
-  <si>
-    <t>0.0007,0.0012,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0045,0.0001,0.0000,0.9988</t>
-  </si>
-  <si>
-    <t>0.8905,0.0030,0.0052,0.0353</t>
+    <t>0.0564,0.0078,0.9145,0.0006</t>
+  </si>
+  <si>
+    <t>0.0048,0.0018,0.9926,0.0000</t>
+  </si>
+  <si>
+    <t>0.0429,0.2447,0.5546,0.0010</t>
+  </si>
+  <si>
+    <t>0.0348,0.0092,0.9298,0.0006</t>
+  </si>
+  <si>
+    <t>0.0496,0.0007,0.9556,0.0002</t>
+  </si>
+  <si>
+    <t>0.0153,0.0002,0.9553,0.0070</t>
+  </si>
+  <si>
+    <t>0.4299,0.0004,0.6566,0.0004</t>
+  </si>
+  <si>
+    <t>0.3101,0.0007,0.7667,0.0002</t>
+  </si>
+  <si>
+    <t>0.9817,0.0001,0.0001,0.0136</t>
+  </si>
+  <si>
+    <t>0.0007,0.0028,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0264,0.0001,0.0001,0.9933</t>
+  </si>
+  <si>
+    <t>0.9559,0.0015,0.0013,0.0100</t>
   </si>
 </sst>
 </file>
@@ -1962,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1976,7 +1979,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2004,7 +2007,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2032,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2043,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
         <v>274</v>
@@ -2071,7 +2074,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
         <v>276</v>
@@ -2197,7 +2200,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
         <v>285</v>
@@ -2393,7 +2396,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>299</v>
@@ -2407,7 +2410,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D40" t="s">
         <v>300</v>
@@ -2729,7 +2732,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D63" t="s">
         <v>323</v>
@@ -2816,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>283</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2830,7 +2833,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2841,10 +2844,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2858,7 +2861,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2872,7 +2875,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2886,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2900,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2914,7 +2917,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2928,7 +2931,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2942,7 +2945,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2956,7 +2959,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2970,7 +2973,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2984,7 +2987,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2998,7 +3001,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3012,7 +3015,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3026,7 +3029,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3040,7 +3043,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3054,7 +3057,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3068,7 +3071,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3079,10 +3082,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3096,7 +3099,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3110,7 +3113,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3124,7 +3127,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3138,7 +3141,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3152,7 +3155,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3166,7 +3169,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3180,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3194,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3264,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3278,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3292,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3306,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>357</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3320,7 +3323,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3334,7 +3337,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3348,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3362,7 +3365,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3376,7 +3379,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3390,7 +3393,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3404,7 +3407,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3418,7 +3421,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3432,7 +3435,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3446,7 +3449,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3460,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3474,7 +3477,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3488,7 +3491,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3502,7 +3505,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3516,7 +3519,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3530,7 +3533,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3544,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3558,7 +3561,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3572,7 +3575,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3583,10 +3586,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3600,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3614,7 +3617,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3628,7 +3631,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3642,7 +3645,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3656,7 +3659,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3670,7 +3673,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3684,7 +3687,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3698,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3712,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3726,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3740,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3751,10 +3754,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3765,10 +3768,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3782,7 +3785,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3796,7 +3799,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3810,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3824,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3835,10 +3838,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3852,7 +3855,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3866,7 +3869,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3880,7 +3883,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>397</v>
+        <v>337</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3894,7 +3897,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3908,7 +3911,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3919,10 +3922,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3936,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3950,7 +3953,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3964,7 +3967,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3978,7 +3981,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3992,7 +3995,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4006,7 +4009,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4020,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4034,7 +4037,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4048,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4062,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4076,7 +4079,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4090,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4104,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4118,7 +4121,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4132,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4146,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4160,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4174,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4188,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>318</v>
+        <v>413</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4202,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>357</v>
+        <v>270</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4216,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>417</v>
+        <v>270</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4230,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4244,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>270</v>
+        <v>415</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4258,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>270</v>
+        <v>384</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4272,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4286,7 +4289,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4300,7 +4303,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4311,10 +4314,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4328,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4342,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4356,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4370,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4384,7 +4387,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4398,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4412,7 +4415,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4426,7 +4429,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4440,7 +4443,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4454,7 +4457,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4468,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4482,7 +4485,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4496,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4510,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4524,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4538,7 +4541,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4552,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4563,10 +4566,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4580,7 +4583,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4594,7 +4597,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4608,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4622,7 +4625,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4636,7 +4639,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4647,10 +4650,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4661,10 +4664,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4678,7 +4681,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4692,7 +4695,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4706,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4720,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4734,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4748,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4762,7 +4765,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4776,7 +4779,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4790,7 +4793,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4804,7 +4807,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4818,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4832,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>357</v>
+        <v>456</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4846,7 +4849,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4860,7 +4863,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>318</v>
+        <v>458</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4874,7 +4877,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>417</v>
+        <v>459</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4888,7 +4891,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>352</v>
+        <v>460</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4902,7 +4905,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4916,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4930,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>270</v>
+        <v>403</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4944,7 +4947,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4958,7 +4961,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4972,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4986,7 +4989,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5000,7 +5003,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5011,10 +5014,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D226" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5028,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5042,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5056,7 +5059,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5070,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5084,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5098,7 +5101,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5112,7 +5115,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5126,7 +5129,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5140,7 +5143,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5154,7 +5157,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>354</v>
+        <v>478</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5168,7 +5171,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>477</v>
+        <v>269</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5182,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5196,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>479</v>
+        <v>456</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5224,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>387</v>
+        <v>481</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5238,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>387</v>
+        <v>456</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5252,7 +5255,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5266,7 +5269,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5280,7 +5283,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5294,7 +5297,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5308,7 +5311,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5322,7 +5325,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5336,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5350,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5364,7 +5367,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5378,7 +5381,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5392,7 +5395,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5406,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5420,7 +5423,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>397</v>
+        <v>337</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5434,7 +5437,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="497">
   <si>
     <t>Filename</t>
   </si>
@@ -808,19 +808,25 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9736,0.0022,0.0072,0.0013</t>
-  </si>
-  <si>
-    <t>0.0021,0.0006,0.0000,0.9993</t>
-  </si>
-  <si>
-    <t>0.9487,0.0004,0.0009,0.0316</t>
-  </si>
-  <si>
-    <t>0.1290,0.0003,0.0004,0.9501</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9419,0.0057,0.0133,0.0047</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.9367,0.0004,0.0003,0.0432</t>
+  </si>
+  <si>
+    <t>0.0093,0.0002,0.0001,0.9973</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
@@ -832,670 +838,673 @@
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.3028,0.0008,0.7543,0.0004</t>
+  </si>
+  <si>
+    <t>0.0080,0.0009,0.9902,0.0001</t>
+  </si>
+  <si>
+    <t>0.5932,0.0019,0.5359,0.0002</t>
+  </si>
+  <si>
+    <t>0.0320,0.0004,0.9690,0.0002</t>
+  </si>
+  <si>
+    <t>0.7501,0.0010,0.3271,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9988,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0320,0.9664,0.0031,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9986,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.4825,0.0040,0.5249,0.0028</t>
+  </si>
+  <si>
+    <t>0.6790,0.0012,0.3570,0.0011</t>
+  </si>
+  <si>
+    <t>0.0059,0.0006,0.9926,0.0001</t>
+  </si>
+  <si>
+    <t>0.0507,0.0005,0.9473,0.0003</t>
+  </si>
+  <si>
+    <t>0.0160,0.0001,0.9880,0.0001</t>
+  </si>
+  <si>
+    <t>0.0085,0.0001,0.9834,0.0019</t>
+  </si>
+  <si>
+    <t>0.0140,0.0001,0.9894,0.0001</t>
+  </si>
+  <si>
+    <t>0.1800,0.8240,0.0084,0.0002</t>
+  </si>
+  <si>
+    <t>0.4630,0.1385,0.2759,0.0011</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9995,0.0008</t>
+  </si>
+  <si>
+    <t>0.0193,0.9660,0.0133,0.0001</t>
+  </si>
+  <si>
+    <t>0.9895,0.0031,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9512,0.0247,0.0153,0.0003</t>
+  </si>
+  <si>
+    <t>0.6462,0.4461,0.0065,0.0003</t>
+  </si>
+  <si>
+    <t>0.0027,0.9671,0.2432,0.0001</t>
+  </si>
+  <si>
+    <t>0.1640,0.3767,0.1036,0.0002</t>
+  </si>
+  <si>
+    <t>0.2296,0.0027,0.7710,0.0013</t>
+  </si>
+  <si>
+    <t>0.1069,0.0029,0.8761,0.0007</t>
+  </si>
+  <si>
+    <t>0.0320,0.0002,0.9673,0.0002</t>
+  </si>
+  <si>
+    <t>0.0275,0.0065,0.9638,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9965,0.0034,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0012,0.9928,0.0011</t>
+  </si>
+  <si>
+    <t>0.0129,0.9085,0.0007,0.4786</t>
+  </si>
+  <si>
+    <t>0.0005,0.9991,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9986,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.0004,0.9949,0.0001</t>
+  </si>
+  <si>
+    <t>0.0176,0.0035,0.9738,0.0001</t>
+  </si>
+  <si>
+    <t>0.0075,0.0005,0.9877,0.0004</t>
+  </si>
+  <si>
+    <t>0.0576,0.0000,0.9635,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.0001,0.9970,0.0002</t>
+  </si>
+  <si>
+    <t>0.0022,0.0007,0.9952,0.0003</t>
+  </si>
+  <si>
+    <t>0.9721,0.0481,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0088,0.0036,0.9939,0.0005</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9929,0.0074,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9680,0.6505,0.0000</t>
+  </si>
+  <si>
+    <t>0.0045,0.0080,0.9858,0.0011</t>
+  </si>
+  <si>
+    <t>0.0097,0.0035,0.9788,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.9914,0.6412,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9980,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9755,0.0011,0.0163,0.0002</t>
+  </si>
+  <si>
+    <t>0.8981,0.0136,0.0629,0.0010</t>
+  </si>
+  <si>
+    <t>0.0013,0.0002,0.9990,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9965,0.6047,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9716,0.7459,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0060,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9527,0.7595,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.0010,0.9994</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.0006,0.9995</t>
+  </si>
+  <si>
+    <t>0.0004,0.0025,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0014,0.9894,0.0637,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9113,0.8830,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9473,0.9319,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9949,0.1191,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.3952,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9922,0.1925,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0017,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0022,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.0001,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0958,0.0017,0.9013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9417,0.0041,0.0158,0.0018</t>
+  </si>
+  <si>
+    <t>0.0200,0.0001,0.9840,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9993,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.9968,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0066,0.9902,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.9985,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.1958,0.8399,0.0048,0.0002</t>
+  </si>
+  <si>
+    <t>0.7540,0.0307,0.1485,0.0025</t>
+  </si>
+  <si>
+    <t>0.4552,0.0005,0.6619,0.0002</t>
+  </si>
+  <si>
+    <t>0.6410,0.0082,0.3537,0.0043</t>
+  </si>
+  <si>
+    <t>0.5309,0.0016,0.5106,0.0017</t>
+  </si>
+  <si>
+    <t>0.0037,0.3214,0.0061,0.9879</t>
+  </si>
+  <si>
+    <t>0.0005,0.9974,0.0147,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9980,0.0004,0.0391</t>
+  </si>
+  <si>
+    <t>0.0001,0.9955,0.7015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.9949,0.0026,0.0000</t>
+  </si>
+  <si>
+    <t>0.6166,0.5226,0.0031,0.0001</t>
+  </si>
+  <si>
+    <t>0.8294,0.2078,0.0157,0.0007</t>
+  </si>
+  <si>
+    <t>0.9987,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.7391,0.9673,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9583,0.9162,0.0000</t>
+  </si>
+  <si>
+    <t>0.0062,0.0019,0.9891,0.0000</t>
+  </si>
+  <si>
+    <t>0.0047,0.0019,0.9888,0.0003</t>
+  </si>
+  <si>
+    <t>0.9662,0.0009,0.0153,0.0005</t>
+  </si>
+  <si>
+    <t>0.9059,0.0015,0.0985,0.0004</t>
+  </si>
+  <si>
+    <t>0.0841,0.0002,0.9378,0.0002</t>
+  </si>
+  <si>
+    <t>0.8843,0.0034,0.1010,0.0009</t>
+  </si>
+  <si>
+    <t>0.0409,0.0003,0.0001,0.9869</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.9796,0.6431,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0002,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0247,0.9765,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.3836,0.7312,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.0353,0.0002,0.0004,0.9857</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0023,0.9964,0.0008</t>
+  </si>
+  <si>
+    <t>0.9920,0.0001,0.0001,0.0032</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.3017,0.6814,0.0224,0.0004</t>
+  </si>
+  <si>
+    <t>0.9735,0.0014,0.0025,0.0042</t>
+  </si>
+  <si>
+    <t>0.9270,0.0369,0.0140,0.0010</t>
+  </si>
+  <si>
+    <t>0.7264,0.0657,0.1303,0.0035</t>
+  </si>
+  <si>
+    <t>0.8713,0.0623,0.0370,0.0006</t>
+  </si>
+  <si>
+    <t>0.8237,0.0310,0.1022,0.0010</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.2562,0.0021,0.7946,0.0002</t>
-  </si>
-  <si>
-    <t>0.1657,0.0011,0.8657,0.0002</t>
-  </si>
-  <si>
-    <t>0.7059,0.0007,0.4431,0.0001</t>
-  </si>
-  <si>
-    <t>0.0868,0.0006,0.9168,0.0004</t>
-  </si>
-  <si>
-    <t>0.7252,0.0016,0.2679,0.0018</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0488,0.9463,0.0068,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.5792,0.0005,0.4781,0.0010</t>
-  </si>
-  <si>
-    <t>0.6395,0.0017,0.4178,0.0007</t>
-  </si>
-  <si>
-    <t>0.0303,0.0005,0.9740,0.0001</t>
-  </si>
-  <si>
-    <t>0.0196,0.0004,0.9755,0.0003</t>
-  </si>
-  <si>
-    <t>0.0398,0.0001,0.9765,0.0000</t>
-  </si>
-  <si>
-    <t>0.1047,0.0001,0.8876,0.0014</t>
-  </si>
-  <si>
-    <t>0.0115,0.0000,0.9908,0.0003</t>
-  </si>
-  <si>
-    <t>0.1621,0.8149,0.0113,0.0001</t>
-  </si>
-  <si>
-    <t>0.6322,0.0330,0.2971,0.0005</t>
-  </si>
-  <si>
-    <t>0.0008,0.0006,0.9990,0.0007</t>
-  </si>
-  <si>
-    <t>0.0052,0.9889,0.0080,0.0001</t>
-  </si>
-  <si>
-    <t>0.9813,0.0077,0.0034,0.0003</t>
-  </si>
-  <si>
-    <t>0.9699,0.0060,0.0133,0.0004</t>
-  </si>
-  <si>
-    <t>0.6644,0.4664,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.0036,0.9712,0.1258,0.0001</t>
-  </si>
-  <si>
-    <t>0.0329,0.8001,0.0927,0.0003</t>
-  </si>
-  <si>
-    <t>0.6145,0.0011,0.4660,0.0006</t>
-  </si>
-  <si>
-    <t>0.0231,0.0292,0.9492,0.0003</t>
-  </si>
-  <si>
-    <t>0.3214,0.0001,0.7676,0.0002</t>
-  </si>
-  <si>
-    <t>0.1644,0.0022,0.8743,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.9940,0.0076,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.0054,0.9888,0.0026</t>
-  </si>
-  <si>
-    <t>0.0019,0.8912,0.0019,0.9786</t>
-  </si>
-  <si>
-    <t>0.0011,0.9979,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.9978,0.0040,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9990,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0375,0.0017,0.9480,0.0003</t>
-  </si>
-  <si>
-    <t>0.0034,0.0023,0.9929,0.0001</t>
-  </si>
-  <si>
-    <t>0.0156,0.0015,0.9664,0.0079</t>
-  </si>
-  <si>
-    <t>0.0176,0.0000,0.9908,0.0000</t>
-  </si>
-  <si>
-    <t>0.0051,0.0003,0.9935,0.0003</t>
-  </si>
-  <si>
-    <t>0.0038,0.0019,0.9911,0.0005</t>
-  </si>
-  <si>
-    <t>0.9887,0.0126,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0008,0.9987,0.0005</t>
-  </si>
-  <si>
-    <t>0.9978,0.0010,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9863,0.0152,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.9831,0.2288,0.0001</t>
-  </si>
-  <si>
-    <t>0.0050,0.0032,0.9884,0.0006</t>
-  </si>
-  <si>
-    <t>0.0198,0.0092,0.9621,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.9902,0.4975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.9958,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.8639,0.0008,0.1834,0.0003</t>
-  </si>
-  <si>
-    <t>0.8088,0.0108,0.1638,0.0006</t>
-  </si>
-  <si>
-    <t>0.0041,0.0027,0.9945,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9959,0.8209,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.9521,0.2739,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.0704,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9908,0.6744,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0008,0.0004,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0002,0.9966,0.0790,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.8810,0.9307,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9779,0.9273,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9912,0.6479,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9819,0.7013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9450,0.7425,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.0000,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0270,0.0005,0.9720,0.0002</t>
-  </si>
-  <si>
-    <t>0.9715,0.0007,0.0120,0.0004</t>
-  </si>
-  <si>
-    <t>0.0037,0.0001,0.9962,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.9987,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9994,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.9954,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0176,0.9779,0.0038,0.0003</t>
-  </si>
-  <si>
-    <t>0.0008,0.9982,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3333,0.7173,0.0086,0.0004</t>
-  </si>
-  <si>
-    <t>0.8201,0.0182,0.1308,0.0016</t>
-  </si>
-  <si>
-    <t>0.1362,0.0056,0.8356,0.0010</t>
-  </si>
-  <si>
-    <t>0.8544,0.0106,0.0994,0.0015</t>
-  </si>
-  <si>
-    <t>0.8348,0.0025,0.2099,0.0004</t>
-  </si>
-  <si>
-    <t>0.0486,0.3483,0.0307,0.8993</t>
-  </si>
-  <si>
-    <t>0.0004,0.9985,0.0052,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0007,0.0040</t>
-  </si>
-  <si>
-    <t>0.0000,0.9946,0.8903,0.0000</t>
-  </si>
-  <si>
-    <t>0.0048,0.9921,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.6625,0.4880,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.7646,0.3286,0.0063,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0011,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9970,0.0006,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.7691,0.8677,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.3019,0.9518,0.0000</t>
-  </si>
-  <si>
-    <t>0.0129,0.0090,0.9690,0.0000</t>
-  </si>
-  <si>
-    <t>0.0136,0.0014,0.9793,0.0001</t>
-  </si>
-  <si>
-    <t>0.9738,0.0007,0.0091,0.0003</t>
-  </si>
-  <si>
-    <t>0.6762,0.0017,0.3703,0.0009</t>
-  </si>
-  <si>
-    <t>0.5476,0.0001,0.5396,0.0005</t>
-  </si>
-  <si>
-    <t>0.6246,0.0018,0.4055,0.0018</t>
-  </si>
-  <si>
-    <t>0.0136,0.0001,0.0001,0.9963</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
+    <t>0.7046,0.3893,0.0064,0.0004</t>
+  </si>
+  <si>
+    <t>0.6048,0.5519,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.4638,0.6715,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.9943,0.0013,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9763,0.0250,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9940,0.0031,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9965,0.0029,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9373,0.0617,0.0111,0.0013</t>
+  </si>
+  <si>
+    <t>0.0022,0.0001,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.9936,0.0031,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0014,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0182,0.0297,0.9455,0.0007</t>
+  </si>
+  <si>
+    <t>0.0022,0.0001,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0238,0.0614,0.9108,0.0005</t>
+  </si>
+  <si>
+    <t>0.0031,0.0010,0.9955,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0000,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0328,0.0041,0.9513,0.0003</t>
+  </si>
+  <si>
+    <t>0.2236,0.0028,0.7916,0.0010</t>
+  </si>
+  <si>
+    <t>0.8964,0.0044,0.0568,0.0022</t>
+  </si>
+  <si>
+    <t>0.3645,0.0250,0.5661,0.0011</t>
+  </si>
+  <si>
+    <t>0.1500,0.1848,0.3960,0.0006</t>
+  </si>
+  <si>
+    <t>0.8751,0.0025,0.1517,0.0003</t>
+  </si>
+  <si>
+    <t>0.4494,0.0099,0.4647,0.0076</t>
+  </si>
+  <si>
+    <t>0.2330,0.0052,0.7845,0.0004</t>
+  </si>
+  <si>
+    <t>0.1006,0.9207,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.0240,0.9805,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.5865,0.5325,0.0045,0.0001</t>
+  </si>
+  <si>
+    <t>0.9875,0.0151,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.1554,0.8980,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.7813,0.1147,0.0055,0.0004</t>
+  </si>
+  <si>
+    <t>0.8402,0.0025,0.1762,0.0009</t>
+  </si>
+  <si>
+    <t>0.9252,0.0035,0.0314,0.0022</t>
+  </si>
+  <si>
+    <t>0.8979,0.0056,0.0657,0.0014</t>
+  </si>
+  <si>
+    <t>0.7786,0.0013,0.2373,0.0010</t>
+  </si>
+  <si>
+    <t>0.0172,0.0001,0.9874,0.0002</t>
+  </si>
+  <si>
+    <t>0.0203,0.0394,0.8981,0.0006</t>
+  </si>
+  <si>
+    <t>0.1695,0.0183,0.7776,0.0005</t>
+  </si>
+  <si>
+    <t>0.0616,0.0027,0.9273,0.0001</t>
+  </si>
+  <si>
+    <t>0.0198,0.4068,0.6063,0.0002</t>
+  </si>
+  <si>
+    <t>0.9946,0.0032,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9956,0.0019,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9926,0.0079,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0001,0.9975,0.0006</t>
+  </si>
+  <si>
+    <t>0.4553,0.1059,0.3362,0.0033</t>
+  </si>
+  <si>
+    <t>0.9473,0.0026,0.0139,0.0080</t>
+  </si>
+  <si>
+    <t>0.0071,0.0001,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0032,0.0007,0.9961,0.0001</t>
+  </si>
+  <si>
+    <t>0.0095,0.0225,0.9619,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0090,0.0019,0.9829,0.0003</t>
+  </si>
+  <si>
+    <t>0.0021,0.0001,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0158,0.0007,0.9774,0.0004</t>
+  </si>
+  <si>
+    <t>0.0374,0.0034,0.9422,0.0015</t>
+  </si>
+  <si>
+    <t>0.7742,0.0036,0.1870,0.0041</t>
+  </si>
+  <si>
+    <t>0.8115,0.0006,0.2029,0.0011</t>
+  </si>
+  <si>
+    <t>0.9773,0.0004,0.0129,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0011,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0017,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9941,0.0068,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0147,0.0523,0.9356,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0345,0.9924,0.0000</t>
+  </si>
+  <si>
+    <t>0.0840,0.0097,0.8648,0.0005</t>
+  </si>
+  <si>
+    <t>0.1025,0.0218,0.8252,0.0005</t>
+  </si>
+  <si>
+    <t>0.0441,0.0003,0.9690,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.0004,0.9934,0.0008</t>
+  </si>
+  <si>
+    <t>0.2489,0.0027,0.7655,0.0006</t>
+  </si>
+  <si>
+    <t>0.3896,0.0022,0.6536,0.0008</t>
+  </si>
+  <si>
+    <t>0.9733,0.0002,0.0001,0.0174</t>
+  </si>
+  <si>
+    <t>0.0028,0.0064,0.0001,0.9987</t>
+  </si>
+  <si>
+    <t>0.0414,0.0001,0.0000,0.9900</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9860,0.7143,0.0000</t>
-  </si>
-  <si>
-    <t>0.9967,0.0009,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0413,0.9613,0.0020,0.0007</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0946,0.9362,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.5568,0.0001,0.0001,0.6056</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0049,0.9976,0.0010</t>
-  </si>
-  <si>
-    <t>0.9737,0.0001,0.0002,0.0176</t>
-  </si>
-  <si>
-    <t>0.9979,0.0000,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.4016,0.5470,0.0392,0.0007</t>
-  </si>
-  <si>
-    <t>0.9735,0.0036,0.0028,0.0017</t>
-  </si>
-  <si>
-    <t>0.9203,0.0362,0.0233,0.0008</t>
-  </si>
-  <si>
-    <t>0.6388,0.0370,0.2651,0.0018</t>
-  </si>
-  <si>
-    <t>0.6761,0.0155,0.2927,0.0013</t>
-  </si>
-  <si>
-    <t>0.9057,0.0618,0.0161,0.0005</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9347,0.0983,0.0049,0.0002</t>
-  </si>
-  <si>
-    <t>0.4870,0.6617,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.3930,0.7212,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.0153,0.0014,0.9861,0.0013</t>
-  </si>
-  <si>
-    <t>0.9754,0.0295,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0007,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0020,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8614,0.1556,0.0186,0.0018</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.9867,0.0117,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0004,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0184,0.0069,0.9647,0.0004</t>
-  </si>
-  <si>
-    <t>0.0070,0.0002,0.9915,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.1836,0.9645,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0041,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0048,0.0001,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.3256,0.0056,0.6898,0.0012</t>
-  </si>
-  <si>
-    <t>0.1580,0.0013,0.8582,0.0009</t>
-  </si>
-  <si>
-    <t>0.7765,0.0260,0.1576,0.0022</t>
-  </si>
-  <si>
-    <t>0.2687,0.0068,0.7383,0.0004</t>
-  </si>
-  <si>
-    <t>0.2825,0.0844,0.3753,0.0004</t>
-  </si>
-  <si>
-    <t>0.8684,0.0039,0.1438,0.0005</t>
-  </si>
-  <si>
-    <t>0.8370,0.0043,0.1081,0.0064</t>
-  </si>
-  <si>
-    <t>0.4172,0.0040,0.6207,0.0010</t>
-  </si>
-  <si>
-    <t>0.0651,0.9389,0.0039,0.0001</t>
-  </si>
-  <si>
-    <t>0.0129,0.9869,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.3315,0.7621,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.8637,0.2388,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.2607,0.8363,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9537,0.0016,0.0225,0.0003</t>
-  </si>
-  <si>
-    <t>0.8507,0.0011,0.1968,0.0004</t>
-  </si>
-  <si>
-    <t>0.7978,0.0043,0.1873,0.0016</t>
-  </si>
-  <si>
-    <t>0.6981,0.0022,0.3191,0.0022</t>
-  </si>
-  <si>
-    <t>0.9065,0.0017,0.0790,0.0008</t>
-  </si>
-  <si>
-    <t>0.0099,0.0003,0.9898,0.0010</t>
-  </si>
-  <si>
-    <t>0.0135,0.0039,0.9682,0.0003</t>
-  </si>
-  <si>
-    <t>0.2956,0.0425,0.5908,0.0017</t>
-  </si>
-  <si>
-    <t>0.1442,0.0021,0.8680,0.0001</t>
-  </si>
-  <si>
-    <t>0.0169,0.0772,0.8771,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9931,0.0052,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9938,0.0068,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0017,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0029,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0104,0.0009,0.9851,0.0023</t>
-  </si>
-  <si>
-    <t>0.1964,0.0937,0.6077,0.0042</t>
-  </si>
-  <si>
-    <t>0.9373,0.0022,0.0141,0.0122</t>
-  </si>
-  <si>
-    <t>0.0407,0.0003,0.9757,0.0000</t>
-  </si>
-  <si>
-    <t>0.0067,0.0003,0.9955,0.0000</t>
-  </si>
-  <si>
-    <t>0.0219,0.8386,0.1789,0.0003</t>
-  </si>
-  <si>
-    <t>0.0037,0.0001,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0602,0.0010,0.9354,0.0004</t>
-  </si>
-  <si>
-    <t>0.0055,0.0005,0.9946,0.0000</t>
-  </si>
-  <si>
-    <t>0.1799,0.0012,0.8372,0.0007</t>
-  </si>
-  <si>
-    <t>0.0088,0.0013,0.9838,0.0006</t>
-  </si>
-  <si>
-    <t>0.8243,0.0023,0.1596,0.0017</t>
-  </si>
-  <si>
-    <t>0.6692,0.0023,0.3232,0.0032</t>
-  </si>
-  <si>
-    <t>0.9817,0.0002,0.0066,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0013,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0023,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0564,0.0078,0.9145,0.0006</t>
-  </si>
-  <si>
-    <t>0.0048,0.0018,0.9926,0.0000</t>
-  </si>
-  <si>
-    <t>0.0429,0.2447,0.5546,0.0010</t>
-  </si>
-  <si>
-    <t>0.0348,0.0092,0.9298,0.0006</t>
-  </si>
-  <si>
-    <t>0.0496,0.0007,0.9556,0.0002</t>
-  </si>
-  <si>
-    <t>0.0153,0.0002,0.9553,0.0070</t>
-  </si>
-  <si>
-    <t>0.4299,0.0004,0.6566,0.0004</t>
-  </si>
-  <si>
-    <t>0.3101,0.0007,0.7667,0.0002</t>
-  </si>
-  <si>
-    <t>0.9817,0.0001,0.0001,0.0136</t>
-  </si>
-  <si>
-    <t>0.0007,0.0028,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0264,0.0001,0.0001,0.9933</t>
-  </si>
-  <si>
-    <t>0.9559,0.0015,0.0013,0.0100</t>
+    <t>0.9618,0.0019,0.0022,0.0078</t>
   </si>
 </sst>
 </file>
@@ -1881,7 +1890,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1895,7 +1904,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1909,7 +1918,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1923,7 +1932,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1937,7 +1946,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1951,7 +1960,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1965,7 +1974,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1993,7 +2002,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2007,7 +2016,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2021,7 +2030,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2035,7 +2044,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2049,7 +2058,7 @@
         <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2063,7 +2072,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2074,10 +2083,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2091,7 +2100,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2105,7 +2114,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2119,7 +2128,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2133,7 +2142,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2147,7 +2156,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2161,7 +2170,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2175,7 +2184,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2186,10 +2195,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2203,7 +2212,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2217,7 +2226,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2231,7 +2240,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2245,7 +2254,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2259,7 +2268,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2273,7 +2282,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2287,7 +2296,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2298,10 +2307,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2315,7 +2324,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2329,7 +2338,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2343,7 +2352,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2357,7 +2366,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2371,7 +2380,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2385,7 +2394,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2396,10 +2405,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2410,10 +2419,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2427,7 +2436,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2441,7 +2450,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2455,7 +2464,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2469,7 +2478,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2483,7 +2492,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2494,10 +2503,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2511,7 +2520,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2525,7 +2534,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2539,7 +2548,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2553,7 +2562,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2567,7 +2576,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2581,7 +2590,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2595,7 +2604,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2609,7 +2618,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2623,7 +2632,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2637,7 +2646,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2651,7 +2660,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2665,7 +2674,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2679,7 +2688,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2693,7 +2702,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2707,7 +2716,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2721,7 +2730,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2732,10 +2741,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2749,7 +2758,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2763,7 +2772,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2774,10 +2783,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2791,7 +2800,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2805,7 +2814,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2819,7 +2828,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>283</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2833,7 +2842,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2847,7 +2856,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2861,7 +2870,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2875,7 +2884,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2886,10 +2895,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2903,7 +2912,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2917,7 +2926,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2931,7 +2940,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2945,7 +2954,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2959,7 +2968,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2973,7 +2982,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2987,7 +2996,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3001,7 +3010,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3015,7 +3024,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3029,7 +3038,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3043,7 +3052,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3054,10 +3063,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3068,10 +3077,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3082,10 +3091,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3099,7 +3108,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3113,7 +3122,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3127,7 +3136,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3141,7 +3150,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3155,7 +3164,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3169,7 +3178,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3183,7 +3192,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3197,7 +3206,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3211,7 +3220,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3225,7 +3234,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>356</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3239,7 +3248,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3253,7 +3262,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3281,7 +3290,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3295,7 +3304,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3309,7 +3318,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3323,7 +3332,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3337,7 +3346,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3351,7 +3360,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3365,7 +3374,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3379,7 +3388,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3393,7 +3402,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3407,7 +3416,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3421,7 +3430,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3435,7 +3444,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3449,7 +3458,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>363</v>
+        <v>281</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3463,7 +3472,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3477,7 +3486,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3491,7 +3500,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3505,7 +3514,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3516,10 +3525,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3533,7 +3542,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3547,7 +3556,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3561,7 +3570,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>371</v>
+        <v>311</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3575,7 +3584,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3589,7 +3598,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3603,7 +3612,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3614,10 +3623,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3631,7 +3640,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3645,7 +3654,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3659,7 +3668,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3673,7 +3682,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3687,7 +3696,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3701,7 +3710,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3715,7 +3724,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3729,7 +3738,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3743,7 +3752,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3757,7 +3766,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3768,10 +3777,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3785,7 +3794,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3799,7 +3808,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3813,7 +3822,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3827,7 +3836,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3841,7 +3850,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3855,7 +3864,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3869,7 +3878,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3883,7 +3892,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>337</v>
+        <v>397</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3897,7 +3906,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3911,7 +3920,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3925,7 +3934,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3939,7 +3948,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3953,7 +3962,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3967,7 +3976,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3981,7 +3990,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3995,7 +4004,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4009,7 +4018,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4023,7 +4032,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4037,7 +4046,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4051,7 +4060,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4065,7 +4074,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4079,7 +4088,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4093,7 +4102,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4107,7 +4116,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4121,7 +4130,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4135,7 +4144,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4149,7 +4158,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4163,7 +4172,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>269</v>
+        <v>384</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4177,7 +4186,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4191,7 +4200,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4205,7 +4214,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>270</v>
+        <v>406</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4219,7 +4228,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>270</v>
+        <v>417</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4233,7 +4242,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4247,7 +4256,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4275,7 +4284,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4286,10 +4295,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D174" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4303,7 +4312,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4314,10 +4323,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4331,7 +4340,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4345,7 +4354,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4359,7 +4368,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4373,7 +4382,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4387,7 +4396,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4401,7 +4410,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4415,7 +4424,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4429,7 +4438,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4443,7 +4452,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4457,7 +4466,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4471,7 +4480,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4485,7 +4494,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4499,7 +4508,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4513,7 +4522,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4527,7 +4536,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4541,7 +4550,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4555,7 +4564,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4566,10 +4575,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D194" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4583,7 +4592,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4594,10 +4603,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D196" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4611,7 +4620,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4625,7 +4634,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4639,7 +4648,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4650,10 +4659,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D200" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4667,7 +4676,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4681,7 +4690,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4695,7 +4704,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4709,7 +4718,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4723,7 +4732,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4737,7 +4746,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4751,7 +4760,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4765,7 +4774,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4779,7 +4788,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4793,7 +4802,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4807,7 +4816,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4821,7 +4830,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4835,7 +4844,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>456</v>
+        <v>403</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4849,7 +4858,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4863,7 +4872,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4877,7 +4886,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4891,7 +4900,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4905,7 +4914,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4919,7 +4928,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>462</v>
+        <v>272</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4933,7 +4942,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4947,7 +4956,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4958,10 +4967,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D222" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4975,7 +4984,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4989,7 +4998,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5003,7 +5012,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5014,10 +5023,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5031,7 +5040,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5045,7 +5054,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5059,7 +5068,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5073,7 +5082,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5087,7 +5096,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5101,7 +5110,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5115,7 +5124,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5129,7 +5138,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5143,7 +5152,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5157,7 +5166,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5171,7 +5180,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5185,7 +5194,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5199,7 +5208,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5213,7 +5222,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5227,7 +5236,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>481</v>
+        <v>358</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5241,7 +5250,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>456</v>
+        <v>417</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5255,7 +5264,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5269,7 +5278,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5283,7 +5292,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5297,7 +5306,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5311,7 +5320,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5325,7 +5334,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5339,7 +5348,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5353,7 +5362,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5367,7 +5376,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5381,7 +5390,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5395,7 +5404,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5409,7 +5418,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>395</v>
+        <v>495</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5423,7 +5432,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>337</v>
+        <v>495</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5437,7 +5446,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
